--- a/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/01_Tasarım Girdileri, Malzeme ve Ürün Ağacı/EKG-TAS-LST-03_urun_agaci_bom_ve_malzeme_teknik_sartlari.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/01_Tasarım Girdileri, Malzeme ve Ürün Ağacı/EKG-TAS-LST-03_urun_agaci_bom_ve_malzeme_teknik_sartlari.xlsx
@@ -844,7 +844,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-LST-03&amp;C&amp;"Arial,Regular"&amp;11Ürün Ağacı BOM ve Malzeme Teknik Şartları</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: BOM teknik kimlik ve revizyona bağlandı; maliyet alanları çıkarılıp boş veri korumalı ağırlık hesabı bırakıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -983,7 +984,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-LST-03&amp;C&amp;"Arial,Regular"&amp;11Ürün Ağacı BOM ve Malzeme Teknik Şartları</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: BOM teknik kimlik ve revizyona bağlandı; maliyet alanları çıkarılıp boş veri korumalı ağırlık hesabı bırakıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>